--- a/courier_app/public/rate_templates/AAA Global Rates May-2026_updated.xlsx
+++ b/courier_app/public/rate_templates/AAA Global Rates May-2026_updated.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="283">
   <si>
     <t xml:space="preserve">AAA Logistics (Pvt) Ltd. </t>
   </si>
@@ -783,6 +783,18 @@
   </si>
   <si>
     <t xml:space="preserve">Additional rates (110-130 CM 25GBP, 131-170 CM 45GBP, 171+ CM 150GBP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For Service provider “Main Land”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-15Kg  for 1Kg rate is 5500 and after 1kg onward to 14 addup 1500 successively </t>
+  </si>
+  <si>
+    <t xml:space="preserve">I.e if 1kg then reate 5500 if 2kg then 7000 If 3kg then rate 8500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16-ownward kg rate per kg is 2000</t>
   </si>
   <si>
     <t xml:space="preserve">Zone 1</t>
@@ -1681,9 +1693,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>151920</xdr:colOff>
+      <xdr:colOff>151560</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>123480</xdr:rowOff>
+      <xdr:rowOff>123120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1697,7 +1709,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="76320"/>
-          <a:ext cx="1525320" cy="980640"/>
+          <a:ext cx="1525680" cy="980280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1723,9 +1735,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>790200</xdr:colOff>
+      <xdr:colOff>789840</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>133200</xdr:rowOff>
+      <xdr:rowOff>132840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1739,7 +1751,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="19080"/>
-          <a:ext cx="1600560" cy="1218960"/>
+          <a:ext cx="1600200" cy="1218600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1765,9 +1777,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1028160</xdr:colOff>
+      <xdr:colOff>1027800</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>114120</xdr:rowOff>
+      <xdr:rowOff>113760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1781,7 +1793,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="1522080" cy="1218960"/>
+          <a:ext cx="1521360" cy="1218600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1807,9 +1819,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>447480</xdr:colOff>
+      <xdr:colOff>447120</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>185040</xdr:rowOff>
+      <xdr:rowOff>184680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1823,7 +1835,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="76320"/>
-          <a:ext cx="1257840" cy="1042200"/>
+          <a:ext cx="1257480" cy="1041840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4454,7 +4466,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D108"/>
-  <sheetFormatPr defaultColWidth="12.55859375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.56640625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
@@ -5772,7 +5784,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B4:I27"/>
+  <dimension ref="B4:I35"/>
   <sheetFormatPr defaultColWidth="9.1171875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="22" width="9.11"/>
@@ -6027,6 +6039,26 @@
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C27" s="56" t="s">
         <v>132</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G31" s="22" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G32" s="22" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G33" s="22" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G35" s="22" t="s">
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -6082,13 +6114,13 @@
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="57" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C8" s="57" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D8" s="57" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6527,112 +6559,112 @@
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="61" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C41" s="61" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D41" s="61" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="62"/>
       <c r="C42" s="63" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D42" s="64" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="57"/>
       <c r="C43" s="57" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D43" s="57" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="62"/>
       <c r="C44" s="64" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D44" s="65" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="57"/>
       <c r="C45" s="57" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D45" s="57" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="62"/>
       <c r="C46" s="64" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D46" s="64" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="57"/>
       <c r="C47" s="57" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D47" s="57" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="62"/>
       <c r="C48" s="64" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D48" s="64" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="57"/>
       <c r="C49" s="57" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D49" s="57" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="62"/>
       <c r="C50" s="64" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D50" s="66"/>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="57"/>
       <c r="C51" s="57" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D51" s="67"/>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="62"/>
       <c r="C52" s="64" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D52" s="66"/>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="68"/>
       <c r="C53" s="68" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="D53" s="69"/>
     </row>
